--- a/Portland_Trail_Blazers_2025-26_stats.xlsx
+++ b/Portland_Trail_Blazers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,63 @@
       </c>
       <c r="Q12" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,6 +1932,63 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1889,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2718,63 @@
       </c>
       <c r="Q12" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2617,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3331,6 +3502,63 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3367,7 +3595,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.09090909090909</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="3">
@@ -3377,7 +3605,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.09090909090909</v>
+        <v>20.91666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3387,7 +3615,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.09090909090909</v>
+        <v>17.66666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3397,7 +3625,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>16.66666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3407,7 +3635,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.09090909090909</v>
+        <v>12.41666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -3417,7 +3645,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.181818181818182</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="8">
@@ -3437,7 +3665,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3</v>
+        <v>5.272727272727272</v>
       </c>
     </row>
     <row r="10">
@@ -3457,7 +3685,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.125</v>
+        <v>4.222222222222222</v>
       </c>
     </row>
     <row r="12">
@@ -3467,7 +3695,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.833333333333333</v>
+        <v>3.857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -3477,7 +3705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.333333333333333</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="14">
@@ -3487,7 +3715,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.333333333333333</v>
+        <v>2.571428571428572</v>
       </c>
     </row>
     <row r="15">
@@ -3543,7 +3771,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.454545454545455</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="3">
@@ -3553,27 +3781,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.636363636363637</v>
+        <v>4.583333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Blake Wesley</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.181818181818182</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Blake Wesley</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.166666666666667</v>
+        <v>2.916666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3583,27 +3811,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.272727272727273</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.545454545454545</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -3613,7 +3841,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.181818181818182</v>
+        <v>1.083333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3629,21 +3857,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="13">
@@ -3653,7 +3881,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -3663,7 +3891,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="15">
@@ -3673,7 +3901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3719,7 +3947,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.909090909090908</v>
+        <v>8.833333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -3729,27 +3957,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.272727272727272</v>
+        <v>6.583333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.363636363636363</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.090909090909091</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
@@ -3759,7 +3987,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3769,7 +3997,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.833333333333333</v>
+        <v>3.714285714285714</v>
       </c>
     </row>
     <row r="8">
@@ -3789,27 +4017,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.909090909090909</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Caleb Love</t>
+          <t>Blake Wesley</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.666666666666667</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blake Wesley</t>
+          <t>Caleb Love</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -3819,7 +4047,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -3839,7 +4067,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -3859,7 +4087,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -3891,21 +4119,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.636363636363636</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.545454545454545</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3915,7 +4143,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.090909090909091</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3925,7 +4153,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3935,7 +4163,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.909090909090909</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3945,7 +4173,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.375</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3965,7 +4193,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -3975,27 +4203,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blake Wesley</t>
+          <t>Kris Murray</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kris Murray</t>
+          <t>Blake Wesley</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -4005,7 +4233,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -4015,7 +4243,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="15">
@@ -4025,7 +4253,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="16">
@@ -4049,7 +4277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,6 +4538,27 @@
         <v>242</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>116</v>
+      </c>
+      <c r="D13" t="n">
+        <v>140</v>
+      </c>
+      <c r="E13" t="n">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
